--- a/astro-site/public/dl/kit-tareas-chocolateria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/BONUS-02-calendario-anual-tareas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -136,47 +138,47 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -536,15 +538,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -552,6 +555,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -580,8 +584,25 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -590,17 +611,17 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="16"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="20"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -937,6 +959,7 @@
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="11" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
@@ -951,10 +974,19 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" type="list">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/BONUS-02-calendario-anual-tareas.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>▸ 15 fechas clave para chocolaterías con preparación especial.</t>
+          <t>▸ Un mes por fila con las 12 campañas y fechas señaladas del año chocolatero español.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,14 @@
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -679,7 +686,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Rebajas post-Navidad, lanzar colección invierno, planificar San Valentín</t>
+          <t>Reyes (6): liquidar turrón y figuras de Navidad · rebajas post-Navidad · lanzar la colección de invierno · planificar San Valentín</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -703,7 +710,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>San Valentín (14), producción corazones y edición limitada, entregas express</t>
+          <t>San Valentín (14): corazones y edición limitada · fecha límite de encargos el día 10 · entregas exprés los días 13 y 14</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -727,7 +734,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Día del Padre (19 España), preparación Pascua, talleres infantiles</t>
+          <t>Día del Padre (19) · preparación de Pascua (fecha móvil) · talleres infantiles de Semana Santa</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -751,7 +758,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Semana Santa / Pascua, monas y huevos, colección primavera</t>
+          <t>Semana Santa y Pascua: monas y huevos · arrancan las COMUNIONES (abril-junio): detalles de mesa, figuras y cajas personalizadas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -775,7 +782,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Día de la Madre (1er domingo), edición regalo premium</t>
+          <t>Día de la Madre (1.er domingo) · pico de COMUNIONES · edición regalo premium</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -799,7 +806,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Inicio verano, adaptar catálogo (menos bombones, más tabletas)</t>
+          <t>Últimas comuniones · inicio del verano: adaptar catálogo (menos ganache fresca, más tableta y producto estable)</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -823,7 +830,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Temporada turística, packs regalo turista, colaboraciones locales</t>
+          <t>Temporada turística: packs souvenir y colaboraciones locales · vigilar a diario la temperatura de tienda y vitrina</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -847,7 +854,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Mantenimiento profundo obrador, vacaciones escalonadas, stock Navidad</t>
+          <t>Asunción (15): festivo nacional, la tienda abre para el turista aunque el obrador pare · mantenimiento profundo · vacaciones escalonadas · cerrar el pedido de coberturas de Navidad</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -871,7 +878,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Vuelta a la rutina, lanzar colección otoño, ferias gastronómicas</t>
+          <t>Vuelta a la rutina · colección de otoño · ferias gastronómicas · abrir la agenda de pedidos corporativos de Navidad</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -895,7 +902,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Halloween (31), producción figuras terror, preparación Navidad intensa</t>
+          <t>Halloween (31): figuras y bombones de temporada · producción navideña a pleno · publicar el catálogo de Navidad</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -919,12 +926,12 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Black Friday, preventa Navidad, producción de turrones y cestas</t>
+          <t>Todos los Santos (1): panellets y huesos de santo bañados · Black Friday (último viernes) · preventa de Navidad · turrones y cestas</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Turrones, cestas corporativas, figuras navideñas</t>
+          <t>Panellets y huesos de santo bañados, turrones, cestas corporativas, figuras navideñas</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -943,7 +950,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>NAVIDAD — máxima producción: turrones, figuras, cestas, regalos corporativos</t>
+          <t>NAVIDAD, máxima producción · puente de la Constitución y la Inmaculada (6-8): fin de semana largo de máxima venta en tienda · fecha límite de encargos y horarios especiales del 24 y el 31</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -974,8 +981,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
